--- a/data/trans_orig/Q5407-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2007</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>50855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>34857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61101</t>
+          <t>59947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>40901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58791</t>
+          <t>57581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90884</t>
+          <t>92537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85606</t>
+          <t>86142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123498</t>
+          <t>124430</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320661</t>
+          <t>320444</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>342403</t>
+          <t>342592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>460002</t>
+          <t>458139</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>496700</t>
+          <t>497844</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>788606</t>
+          <t>787887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>832095</t>
+          <t>831035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76777</t>
+          <t>76708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85795</t>
+          <t>86169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>48444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>59842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130203</t>
+          <t>130387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143956</t>
+          <t>143813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>22,06%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1274</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6412</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7520</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>7583</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53122</t>
+          <t>53224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>65421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51829</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53112</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98609</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101932</t>
+          <t>99345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143944</t>
+          <t>142200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>437973</t>
+          <t>437558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>462787</t>
+          <t>462859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>537075</t>
+          <t>537481</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>576837</t>
+          <t>578079</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>984044</t>
+          <t>985298</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1031457</t>
+          <t>1035390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2012</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45122</t>
+          <t>45584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66487</t>
+          <t>66578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102526</t>
+          <t>100174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94129</t>
+          <t>94889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133571</t>
+          <t>136320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33033</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61331</t>
+          <t>60559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70865</t>
+          <t>68412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106476</t>
+          <t>105451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108827</t>
+          <t>111296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156285</t>
+          <t>156277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>318774</t>
+          <t>319015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354472</t>
+          <t>354634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440545</t>
+          <t>440952</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>485505</t>
+          <t>487831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>773620</t>
+          <t>768970</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>833231</t>
+          <t>829318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32710</t>
+          <t>33015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100320</t>
+          <t>100148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>113574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59336</t>
+          <t>58579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73695</t>
+          <t>73635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163502</t>
+          <t>163611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184245</t>
+          <t>183650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46786</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49044</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71135</t>
+          <t>70456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106546</t>
+          <t>107281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101120</t>
+          <t>99433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144057</t>
+          <t>146878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40749</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73353</t>
+          <t>72759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84628</t>
+          <t>83820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121789</t>
+          <t>122534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>135599</t>
+          <t>133752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182679</t>
+          <t>182675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>449764</t>
+          <t>450990</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>488342</t>
+          <t>487987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>524456</t>
+          <t>524232</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>573219</t>
+          <t>574110</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>989500</t>
+          <t>986784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1049734</t>
+          <t>1052207</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2016</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36273</t>
+          <t>36571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67124</t>
+          <t>68662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57990</t>
+          <t>55559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93731</t>
+          <t>91863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31780</t>
+          <t>31527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>53684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83716</t>
+          <t>85017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125798</t>
+          <t>124855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122591</t>
+          <t>122171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169280</t>
+          <t>169655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>275375</t>
+          <t>276281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302579</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>379632</t>
+          <t>377337</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>425649</t>
+          <t>424710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>663402</t>
+          <t>663460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>718185</t>
+          <t>717457</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>20429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>19024</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>40620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>48856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169452</t>
+          <t>168780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183852</t>
+          <t>183261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141585</t>
+          <t>142248</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166099</t>
+          <t>165157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>316580</t>
+          <t>316374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345496</t>
+          <t>344706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,62 +5790,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>8212</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>9009</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>32342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>40591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>32647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60689</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72392</t>
+          <t>72689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>22448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44149</t>
+          <t>44081</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41028</t>
+          <t>40900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73441</t>
+          <t>72073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68046</t>
+          <t>69186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107157</t>
+          <t>107108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39273</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64356</t>
+          <t>64877</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109871</t>
+          <t>112873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157503</t>
+          <t>158087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>158207</t>
+          <t>157501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211134</t>
+          <t>210331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>490212</t>
+          <t>489540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>520739</t>
+          <t>521949</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>561292</t>
+          <t>559537</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>612437</t>
+          <t>611688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1062554</t>
+          <t>1063213</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1123416</t>
+          <t>1122069</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2023</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36952</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68985</t>
+          <t>69237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92602</t>
+          <t>92408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94163</t>
+          <t>96743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122945</t>
+          <t>123928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48561</t>
+          <t>48683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106473</t>
+          <t>106571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134615</t>
+          <t>134594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143398</t>
+          <t>142988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177042</t>
+          <t>174621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190473</t>
+          <t>190232</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>211658</t>
+          <t>211680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>283157</t>
+          <t>283980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>314243</t>
+          <t>312840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>481816</t>
+          <t>480491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>517562</t>
+          <t>516776</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29064</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54054</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68047</t>
+          <t>68204</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>236452</t>
+          <t>237865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>252985</t>
+          <t>253119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>375232</t>
+          <t>376446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>442318</t>
+          <t>442480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>628625</t>
+          <t>628470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>703273</t>
+          <t>697425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93647</t>
+          <t>93847</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>101654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60710</t>
+          <t>61074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67815</t>
+          <t>67814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156995</t>
+          <t>157685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167867</t>
+          <t>167772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>31008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49052</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123543</t>
+          <t>123551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86829</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159805</t>
+          <t>160147</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49653</t>
+          <t>50199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73745</t>
+          <t>75414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198257</t>
+          <t>197966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133909</t>
+          <t>139450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250192</t>
+          <t>252436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>531043</t>
+          <t>529698</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560083</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>706990</t>
+          <t>709104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>891761</t>
+          <t>894275</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1266693</t>
+          <t>1265535</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1459701</t>
+          <t>1441572</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5407-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25588</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50855</t>
+          <t>49978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34857</t>
+          <t>33711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59947</t>
+          <t>61474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40901</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>58236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92537</t>
+          <t>90875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86142</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124430</t>
+          <t>123614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320444</t>
+          <t>318359</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>342592</t>
+          <t>341458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>458139</t>
+          <t>458409</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>497844</t>
+          <t>496479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>787887</t>
+          <t>785612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>831035</t>
+          <t>832217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76708</t>
+          <t>77288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86169</t>
+          <t>85645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48444</t>
+          <t>48942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59842</t>
+          <t>59882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130387</t>
+          <t>130778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143813</t>
+          <t>143572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53224</t>
+          <t>53741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65421</t>
+          <t>65192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>55443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99112</t>
+          <t>97670</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99345</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142200</t>
+          <t>141687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>437558</t>
+          <t>435923</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>462859</t>
+          <t>462814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>537481</t>
+          <t>535947</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>578079</t>
+          <t>577143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>985298</t>
+          <t>985709</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1035390</t>
+          <t>1033098</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45584</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66578</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100174</t>
+          <t>99448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>94740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136320</t>
+          <t>135254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32738</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60559</t>
+          <t>62517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68412</t>
+          <t>69282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105451</t>
+          <t>106667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>110967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156277</t>
+          <t>154809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>319015</t>
+          <t>319185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354634</t>
+          <t>352836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440952</t>
+          <t>441687</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>487831</t>
+          <t>488083</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>768970</t>
+          <t>773730</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>829318</t>
+          <t>832195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>15227</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33015</t>
+          <t>32437</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100148</t>
+          <t>100707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113574</t>
+          <t>113541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>57672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>72967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163611</t>
+          <t>163752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183650</t>
+          <t>184263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49318</t>
+          <t>48046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70456</t>
+          <t>69950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107281</t>
+          <t>107370</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99433</t>
+          <t>99835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146878</t>
+          <t>142150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72759</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83820</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>123933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133752</t>
+          <t>133884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182675</t>
+          <t>182688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>450990</t>
+          <t>449916</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>487987</t>
+          <t>487638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>524232</t>
+          <t>525597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>574110</t>
+          <t>573788</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>986784</t>
+          <t>989764</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1052207</t>
+          <t>1051803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68662</t>
+          <t>66804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>55251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91863</t>
+          <t>91948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53684</t>
+          <t>52845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>83722</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124855</t>
+          <t>123944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122171</t>
+          <t>120713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169655</t>
+          <t>167845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>276281</t>
+          <t>277495</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>303877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>377337</t>
+          <t>375793</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>424710</t>
+          <t>422818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>663460</t>
+          <t>664308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>717457</t>
+          <t>718714</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>18656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>42299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48856</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168780</t>
+          <t>168199</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183261</t>
+          <t>183072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142248</t>
+          <t>141633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165157</t>
+          <t>166246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>316374</t>
+          <t>317258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344706</t>
+          <t>344916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72689</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40900</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72073</t>
+          <t>72796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69186</t>
+          <t>68919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107108</t>
+          <t>107687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39255</t>
+          <t>38634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64877</t>
+          <t>65361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112873</t>
+          <t>113396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158087</t>
+          <t>157259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>157501</t>
+          <t>156947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210331</t>
+          <t>209255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>489540</t>
+          <t>489957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>521949</t>
+          <t>520943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>559537</t>
+          <t>560212</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>611688</t>
+          <t>611912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1063213</t>
+          <t>1066524</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1122069</t>
+          <t>1125761</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28228</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>79914</t>
+          <t>86726</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69237</t>
+          <t>74248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>100428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>108142</t>
+          <t>115786</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96743</t>
+          <t>101457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123928</t>
+          <t>131471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38324</t>
+          <t>41575</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48683</t>
+          <t>52612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120256</t>
+          <t>130047</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106571</t>
+          <t>116467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134594</t>
+          <t>144636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>158580</t>
+          <t>171622</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142988</t>
+          <t>154912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174621</t>
+          <t>190703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>201961</t>
+          <t>218456</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190232</t>
+          <t>206096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>211680</t>
+          <t>230323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>297981</t>
+          <t>319616</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>283980</t>
+          <t>302729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>312840</t>
+          <t>335956</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>499942</t>
+          <t>538072</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>480491</t>
+          <t>518352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>516776</t>
+          <t>559878</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>289091</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>289091</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>289091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>498151</t>
+          <t>536389</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>498151</t>
+          <t>536389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>498151</t>
+          <t>536389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>766664</t>
+          <t>825480</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>766664</t>
+          <t>825480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>766664</t>
+          <t>825480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>16569</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>45593</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>40126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68204</t>
+          <t>60152</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>246155</t>
+          <t>275232</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237865</t>
+          <t>265517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253119</t>
+          <t>282431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>414558</t>
+          <t>230457</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>376446</t>
+          <t>219837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>442480</t>
+          <t>238267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>660713</t>
+          <t>505690</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>628470</t>
+          <t>491398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>697425</t>
+          <t>516819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>659</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>98510</t>
+          <t>111733</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93847</t>
+          <t>106473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101654</t>
+          <t>115133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>64856</t>
+          <t>74687</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61074</t>
+          <t>69698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67814</t>
+          <t>78222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>163366</t>
+          <t>186421</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157685</t>
+          <t>179932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167772</t>
+          <t>191639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>40991</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>94659</t>
+          <t>103954</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49566</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123551</t>
+          <t>119160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>133874</t>
+          <t>144945</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>128203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160147</t>
+          <t>163447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50199</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75414</t>
+          <t>78889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>153162</t>
+          <t>168175</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>150707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197966</t>
+          <t>184228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>214076</t>
+          <t>233559</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139450</t>
+          <t>214123</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252436</t>
+          <t>256882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546626</t>
+          <t>605421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>529698</t>
+          <t>588720</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560138</t>
+          <t>620717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>777395</t>
+          <t>624761</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>605088</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>894275</t>
+          <t>647344</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1324021</t>
+          <t>1230182</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1265535</t>
+          <t>1204333</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1441572</t>
+          <t>1255221</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>646756</t>
+          <t>711797</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>646756</t>
+          <t>711797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>646756</t>
+          <t>711797</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1025215</t>
+          <t>896890</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1025215</t>
+          <t>896890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1025215</t>
+          <t>896890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1671971</t>
+          <t>1608687</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1671971</t>
+          <t>1608687</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1671971</t>
+          <t>1608687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
